--- a/docs/assets/gestion-ti/business-case.xlsx
+++ b/docs/assets/gestion-ti/business-case.xlsx
@@ -1212,7 +1212,7 @@
         <v>4</v>
       </c>
       <c r="G33" t="str">
-        <v>Pre-matrícula 24/7 desde el sitio público (hoy bloqueada en producción por las reglas desactualizadas). Medir con el origen de cada matrícula.</v>
+        <v>Pre-matrícula 24/7 desde el sitio público (desbloqueada en producción el 2026-10-24 al publicar las reglas corregidas). Medir con el origen de cada matrícula.</v>
       </c>
       <c r="H33" t="str">
         <v>Supuesto a validar</v>

--- a/docs/assets/gestion-ti/business-case.xlsx
+++ b/docs/assets/gestion-ti/business-case.xlsx
@@ -1451,7 +1451,7 @@
         <v>2</v>
       </c>
       <c r="G43" t="str">
-        <v>Actualización de dependencias y correcciones; el CI con 90 pruebas reduce el esfuerzo de verificación.</v>
+        <v>Actualización de dependencias y correcciones; el CI con 99 pruebas reduce el esfuerzo de verificación.</v>
       </c>
       <c r="H43" t="str">
         <v>Supuesto a validar</v>
